--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soPrice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soPrice.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>单据编号</t>
   </si>
@@ -77,6 +77,9 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>明细备注</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
@@ -1325,11 +1331,11 @@
     <col min="8" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="15" max="15" width="21.75" customWidth="1"/>
+    <col min="16" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:16">
+    <row r="1" ht="15" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,55 +1384,61 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
